--- a/input/Documentenlijst.xlsx
+++ b/input/Documentenlijst.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ronaldkoenis/eclipse-workspace/maakmdto/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073D5796-9CD0-AA49-A8B6-E7B4A2458FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113329B7-A172-B840-BDDD-E653EAE80EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6940" yWindow="-27480" windowWidth="39100" windowHeight="17960" xr2:uid="{CD58AC6D-95E4-3D46-BF36-5AD7BB9721C7}"/>
+    <workbookView xWindow="7700" yWindow="-27480" windowWidth="32720" windowHeight="26440" xr2:uid="{CD58AC6D-95E4-3D46-BF36-5AD7BB9721C7}"/>
   </bookViews>
   <sheets>
     <sheet name="documentenlijst" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="196">
   <si>
     <t>agendapunt</t>
   </si>
@@ -596,9 +596,6 @@
     <t>Programmabegroting 2018 (Def. na raad 20171107 - incl. A1 + A3).pdf</t>
   </si>
   <si>
-    <t>Bewerking</t>
-  </si>
-  <si>
     <t>Scans</t>
   </si>
   <si>
@@ -612,6 +609,18 @@
   </si>
   <si>
     <t>audiotulen.aac</t>
+  </si>
+  <si>
+    <t>Geheim</t>
+  </si>
+  <si>
+    <t>geheim</t>
+  </si>
+  <si>
+    <t>Testnotulen van een geheime vergadering.pdf</t>
+  </si>
+  <si>
+    <t>geheimedocs</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1545,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>164</v>
@@ -1559,7 +1568,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>178</v>
@@ -1579,7 +1588,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>177</v>
@@ -1599,7 +1608,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>175</v>
@@ -1619,7 +1628,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>166</v>
@@ -1639,7 +1648,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>167</v>
@@ -1659,7 +1668,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>168</v>
@@ -1679,7 +1688,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>179</v>
@@ -1699,7 +1708,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>180</v>
@@ -1719,7 +1728,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>181</v>
@@ -1739,7 +1748,7 @@
         <v>13</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>182</v>
@@ -1759,7 +1768,7 @@
         <v>15</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>183</v>
@@ -1779,7 +1788,7 @@
         <v>16</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>184</v>
@@ -1799,7 +1808,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>169</v>
@@ -1819,7 +1828,7 @@
         <v>22</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>170</v>
@@ -1839,7 +1848,7 @@
         <v>23</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>171</v>
@@ -1859,7 +1868,7 @@
         <v>24</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>172</v>
@@ -1879,7 +1888,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>173</v>
@@ -1899,7 +1908,7 @@
         <v>26</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>174</v>
@@ -1919,7 +1928,7 @@
         <v>8</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>185</v>
@@ -1939,7 +1948,7 @@
         <v>9</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>186</v>
@@ -1959,7 +1968,7 @@
         <v>27</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" ref="G22:G26" si="0">C22&amp;".pdf"</f>
@@ -1980,7 +1989,7 @@
         <v>28</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" si="0"/>
@@ -2001,7 +2010,7 @@
         <v>30</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" si="0"/>
@@ -2021,7 +2030,15 @@
       <c r="D25" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="4"/>
+      <c r="E25" t="s">
+        <v>193</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G25" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
@@ -2037,7 +2054,7 @@
         <v>32</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" si="0"/>
@@ -2058,7 +2075,7 @@
         <v>34</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G27" t="str">
         <f>C27&amp;".pdf"</f>
@@ -2079,7 +2096,7 @@
         <v>35</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G28" t="str">
         <f>C28&amp;".pdf"</f>
@@ -2118,7 +2135,7 @@
         <v>37</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" ref="G30:G61" si="1">C30&amp;".pdf"</f>
@@ -2139,7 +2156,7 @@
         <v>38</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="1"/>
@@ -2160,7 +2177,7 @@
         <v>39</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="1"/>
@@ -2181,7 +2198,7 @@
         <v>40</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="1"/>
@@ -2202,7 +2219,7 @@
         <v>41</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="1"/>
@@ -2223,7 +2240,7 @@
         <v>42</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G35" t="str">
         <f t="shared" si="1"/>
@@ -2244,7 +2261,7 @@
         <v>43</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G36" t="str">
         <f t="shared" si="1"/>
@@ -2265,7 +2282,7 @@
         <v>44</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="1"/>
@@ -2286,7 +2303,7 @@
         <v>45</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G38" t="str">
         <f t="shared" si="1"/>
@@ -2307,7 +2324,7 @@
         <v>46</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="1"/>
@@ -2328,7 +2345,7 @@
         <v>47</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G40" t="str">
         <f t="shared" si="1"/>
@@ -2349,7 +2366,7 @@
         <v>48</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G41" t="str">
         <f t="shared" si="1"/>
@@ -2370,7 +2387,7 @@
         <v>49</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G42" t="str">
         <f t="shared" si="1"/>
@@ -2391,7 +2408,7 @@
         <v>50</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G43" t="str">
         <f t="shared" si="1"/>
@@ -2412,7 +2429,7 @@
         <v>51</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G44" t="str">
         <f t="shared" si="1"/>
@@ -2433,7 +2450,7 @@
         <v>52</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G45" t="str">
         <f t="shared" si="1"/>
@@ -2454,7 +2471,7 @@
         <v>53</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G46" t="str">
         <f t="shared" si="1"/>
@@ -2475,7 +2492,7 @@
         <v>54</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G47" t="str">
         <f t="shared" si="1"/>
@@ -2496,7 +2513,7 @@
         <v>55</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G48" t="str">
         <f t="shared" si="1"/>
@@ -2517,7 +2534,7 @@
         <v>56</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G49" t="str">
         <f t="shared" si="1"/>
@@ -2538,7 +2555,7 @@
         <v>57</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G50" t="str">
         <f t="shared" si="1"/>
@@ -2559,7 +2576,7 @@
         <v>58</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G51" t="str">
         <f t="shared" si="1"/>
@@ -2580,7 +2597,7 @@
         <v>59</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G52" t="str">
         <f t="shared" si="1"/>
@@ -2601,7 +2618,7 @@
         <v>60</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G53" t="str">
         <f t="shared" si="1"/>
@@ -2622,7 +2639,7 @@
         <v>61</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G54" t="str">
         <f t="shared" si="1"/>
@@ -2643,7 +2660,7 @@
         <v>62</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G55" t="str">
         <f t="shared" si="1"/>
@@ -2664,7 +2681,7 @@
         <v>63</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G56" t="str">
         <f t="shared" si="1"/>
@@ -2685,7 +2702,7 @@
         <v>64</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G57" t="str">
         <f t="shared" si="1"/>
@@ -2706,7 +2723,7 @@
         <v>65</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G58" t="str">
         <f t="shared" si="1"/>
@@ -2727,7 +2744,7 @@
         <v>66</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G59" t="str">
         <f t="shared" si="1"/>
@@ -2748,7 +2765,7 @@
         <v>67</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G60" t="str">
         <f t="shared" si="1"/>
@@ -2769,7 +2786,7 @@
         <v>68</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G61" t="str">
         <f t="shared" si="1"/>
@@ -2790,7 +2807,7 @@
         <v>69</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G62" t="str">
         <f t="shared" ref="G62:G86" si="2">C62&amp;".pdf"</f>
@@ -2811,7 +2828,7 @@
         <v>70</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G63" t="str">
         <f t="shared" si="2"/>
@@ -2832,7 +2849,7 @@
         <v>71</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G64" t="str">
         <f t="shared" si="2"/>
@@ -2853,7 +2870,7 @@
         <v>72</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G65" t="str">
         <f t="shared" si="2"/>
@@ -2874,7 +2891,7 @@
         <v>73</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G66" t="str">
         <f t="shared" si="2"/>
@@ -2895,7 +2912,7 @@
         <v>74</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G67" t="str">
         <f t="shared" si="2"/>
@@ -2916,7 +2933,7 @@
         <v>75</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G68" t="str">
         <f t="shared" si="2"/>
@@ -2937,7 +2954,7 @@
         <v>76</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G69" t="str">
         <f t="shared" si="2"/>
@@ -2958,7 +2975,7 @@
         <v>77</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G70" t="str">
         <f t="shared" si="2"/>
@@ -2979,7 +2996,7 @@
         <v>78</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G71" t="str">
         <f t="shared" si="2"/>
@@ -3000,7 +3017,7 @@
         <v>79</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G72" t="str">
         <f t="shared" si="2"/>
@@ -3021,7 +3038,7 @@
         <v>80</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G73" t="str">
         <f t="shared" si="2"/>
@@ -3042,7 +3059,7 @@
         <v>81</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G74" t="str">
         <f t="shared" si="2"/>
@@ -3063,7 +3080,7 @@
         <v>82</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G75" t="str">
         <f t="shared" si="2"/>
@@ -3084,7 +3101,7 @@
         <v>83</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G76" t="str">
         <f t="shared" si="2"/>
@@ -3105,7 +3122,7 @@
         <v>84</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G77" t="str">
         <f t="shared" si="2"/>
@@ -3126,7 +3143,7 @@
         <v>85</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G78" t="str">
         <f t="shared" si="2"/>
@@ -3147,7 +3164,7 @@
         <v>86</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G79" t="str">
         <f t="shared" si="2"/>
@@ -3168,7 +3185,7 @@
         <v>87</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G80" t="str">
         <f t="shared" si="2"/>
@@ -3189,7 +3206,7 @@
         <v>88</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G81" t="str">
         <f t="shared" si="2"/>
@@ -3210,7 +3227,7 @@
         <v>89</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G82" t="str">
         <f t="shared" si="2"/>
@@ -3231,7 +3248,7 @@
         <v>90</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G83" t="str">
         <f t="shared" si="2"/>
@@ -3252,7 +3269,7 @@
         <v>91</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G84" t="str">
         <f t="shared" si="2"/>
@@ -3273,7 +3290,7 @@
         <v>92</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G85" t="str">
         <f t="shared" si="2"/>
@@ -3294,7 +3311,7 @@
         <v>93</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G86" t="str">
         <f t="shared" si="2"/>
@@ -3315,7 +3332,7 @@
         <v>94</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G87" t="str">
         <f t="shared" ref="G87:G150" si="3">C87&amp;".pdf"</f>
@@ -3336,7 +3353,7 @@
         <v>95</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G88" t="str">
         <f t="shared" si="3"/>
@@ -3357,7 +3374,7 @@
         <v>96</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G89" t="str">
         <f t="shared" si="3"/>
@@ -3378,7 +3395,7 @@
         <v>97</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G90" t="str">
         <f t="shared" si="3"/>
@@ -3399,7 +3416,7 @@
         <v>98</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G91" t="str">
         <f t="shared" si="3"/>
@@ -3420,7 +3437,7 @@
         <v>99</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G92" t="str">
         <f t="shared" si="3"/>
@@ -3441,7 +3458,7 @@
         <v>100</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G93" t="str">
         <f t="shared" si="3"/>
@@ -3462,7 +3479,7 @@
         <v>101</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G94" t="str">
         <f t="shared" si="3"/>
@@ -3483,7 +3500,7 @@
         <v>102</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G95" t="str">
         <f t="shared" si="3"/>
@@ -3504,7 +3521,7 @@
         <v>103</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G96" t="str">
         <f t="shared" si="3"/>
@@ -3525,7 +3542,7 @@
         <v>104</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G97" t="str">
         <f t="shared" si="3"/>
@@ -3546,7 +3563,7 @@
         <v>105</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G98" t="str">
         <f t="shared" si="3"/>
@@ -3567,7 +3584,7 @@
         <v>106</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G99" t="str">
         <f t="shared" si="3"/>
@@ -3588,7 +3605,7 @@
         <v>107</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G100" t="str">
         <f t="shared" si="3"/>
@@ -3609,7 +3626,7 @@
         <v>108</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G101" t="str">
         <f t="shared" si="3"/>
@@ -3630,7 +3647,7 @@
         <v>109</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G102" t="str">
         <f t="shared" si="3"/>
@@ -3651,7 +3668,7 @@
         <v>110</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G103" t="str">
         <f t="shared" si="3"/>
@@ -3672,7 +3689,7 @@
         <v>111</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G104" t="str">
         <f t="shared" si="3"/>
@@ -3693,7 +3710,7 @@
         <v>112</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G105" t="str">
         <f t="shared" si="3"/>
@@ -3714,7 +3731,7 @@
         <v>113</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G106" t="str">
         <f t="shared" si="3"/>
@@ -3735,7 +3752,7 @@
         <v>114</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G107" t="str">
         <f t="shared" si="3"/>
@@ -3756,7 +3773,7 @@
         <v>115</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G108" t="str">
         <f t="shared" si="3"/>
@@ -3777,7 +3794,7 @@
         <v>116</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G109" t="str">
         <f t="shared" si="3"/>
@@ -3798,7 +3815,7 @@
         <v>117</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G110" t="str">
         <f t="shared" si="3"/>
@@ -3819,7 +3836,7 @@
         <v>118</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G111" t="str">
         <f t="shared" si="3"/>
@@ -3840,7 +3857,7 @@
         <v>119</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G112" t="str">
         <f t="shared" si="3"/>
@@ -3861,7 +3878,7 @@
         <v>120</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G113" t="str">
         <f t="shared" si="3"/>
@@ -3882,7 +3899,7 @@
         <v>121</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G114" t="str">
         <f t="shared" si="3"/>
@@ -3903,7 +3920,7 @@
         <v>122</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G115" t="str">
         <f t="shared" si="3"/>
@@ -3924,7 +3941,7 @@
         <v>123</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G116" t="str">
         <f t="shared" si="3"/>
@@ -3945,7 +3962,7 @@
         <v>124</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G117" t="str">
         <f t="shared" si="3"/>
@@ -3966,7 +3983,7 @@
         <v>125</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G118" t="str">
         <f t="shared" si="3"/>
@@ -3987,7 +4004,7 @@
         <v>126</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G119" t="str">
         <f t="shared" si="3"/>
@@ -4008,7 +4025,7 @@
         <v>127</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G120" t="str">
         <f t="shared" si="3"/>
@@ -4029,7 +4046,7 @@
         <v>128</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G121" t="str">
         <f t="shared" si="3"/>
@@ -4050,7 +4067,7 @@
         <v>129</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G122" t="str">
         <f t="shared" si="3"/>
@@ -4071,7 +4088,7 @@
         <v>130</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G123" t="str">
         <f t="shared" si="3"/>
@@ -4092,7 +4109,7 @@
         <v>131</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G124" t="str">
         <f t="shared" si="3"/>
@@ -4113,7 +4130,7 @@
         <v>132</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G125" t="str">
         <f t="shared" si="3"/>
@@ -4134,7 +4151,7 @@
         <v>133</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G126" t="str">
         <f t="shared" si="3"/>
@@ -4155,7 +4172,7 @@
         <v>134</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G127" t="str">
         <f t="shared" si="3"/>
@@ -4176,7 +4193,7 @@
         <v>135</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G128" t="str">
         <f t="shared" si="3"/>
@@ -4197,7 +4214,7 @@
         <v>136</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G129" t="str">
         <f t="shared" si="3"/>
@@ -4218,7 +4235,7 @@
         <v>137</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G130" t="str">
         <f t="shared" si="3"/>
@@ -4239,7 +4256,7 @@
         <v>138</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G131" t="str">
         <f t="shared" si="3"/>
@@ -4260,7 +4277,7 @@
         <v>139</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G132" t="str">
         <f t="shared" si="3"/>
@@ -4281,7 +4298,7 @@
         <v>140</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G133" t="str">
         <f t="shared" si="3"/>
@@ -4302,7 +4319,7 @@
         <v>142</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G134" t="str">
         <f t="shared" si="3"/>
@@ -4323,7 +4340,7 @@
         <v>143</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G135" t="str">
         <f t="shared" si="3"/>
@@ -4344,7 +4361,7 @@
         <v>144</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G136" t="str">
         <f t="shared" si="3"/>
@@ -4365,7 +4382,7 @@
         <v>145</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G137" t="str">
         <f t="shared" si="3"/>
@@ -4386,7 +4403,7 @@
         <v>146</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G138" t="str">
         <f t="shared" si="3"/>
@@ -4407,7 +4424,7 @@
         <v>147</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G139" t="str">
         <f t="shared" si="3"/>
@@ -4428,7 +4445,7 @@
         <v>148</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G140" t="str">
         <f t="shared" si="3"/>
@@ -4449,7 +4466,7 @@
         <v>149</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G141" t="str">
         <f t="shared" si="3"/>
@@ -4470,7 +4487,7 @@
         <v>150</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G142" t="str">
         <f t="shared" si="3"/>
@@ -4491,7 +4508,7 @@
         <v>151</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G143" t="str">
         <f t="shared" si="3"/>
@@ -4512,7 +4529,7 @@
         <v>152</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G144" t="str">
         <f t="shared" si="3"/>
@@ -4533,7 +4550,7 @@
         <v>153</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G145" t="str">
         <f t="shared" si="3"/>
@@ -4554,7 +4571,7 @@
         <v>154</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G146" t="str">
         <f t="shared" si="3"/>
@@ -4575,7 +4592,7 @@
         <v>155</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G147" t="str">
         <f t="shared" si="3"/>
@@ -4596,7 +4613,7 @@
         <v>156</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G148" t="str">
         <f t="shared" si="3"/>
@@ -4617,7 +4634,7 @@
         <v>157</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G149" t="str">
         <f t="shared" si="3"/>
@@ -4638,7 +4655,7 @@
         <v>158</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G150" t="str">
         <f t="shared" si="3"/>
@@ -4659,7 +4676,7 @@
         <v>159</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G151" t="str">
         <f t="shared" ref="G151:G154" si="4">C151&amp;".pdf"</f>
@@ -4680,7 +4697,7 @@
         <v>160</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G152" t="str">
         <f t="shared" si="4"/>
@@ -4701,7 +4718,7 @@
         <v>161</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G153" t="str">
         <f t="shared" si="4"/>
@@ -4722,7 +4739,7 @@
         <v>162</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G154" t="str">
         <f t="shared" si="4"/>
@@ -4732,24 +4749,24 @@
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="C155" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F155" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G155" t="s">
         <v>188</v>
-      </c>
-      <c r="G155" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C156" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G156" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
